--- a/output/Data and Chart Outputs/china_nea_consumption_monthly.xlsx
+++ b/output/Data and Chart Outputs/china_nea_consumption_monthly.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Chart" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Chart - electricity use growth " sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Chart - electricity use growth" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Data" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Jan-Feb" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="YTD" sheetId="6" state="visible" r:id="rId6"/>
@@ -379,7 +379,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>China electricity use growth y/y (NEA) (to Aug/26)</a:t>
+              <a:t>China electricity use growth (NEA) (to Aug/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -394,7 +394,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Chart - electricity use growth '!B1</f>
+              <f>'Chart - electricity use growth'!B1</f>
             </strRef>
           </tx>
           <spPr>
@@ -415,12 +415,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - electricity use growth '!$A$2:$A$54</f>
+              <f>'Chart - electricity use growth'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - electricity use growth '!$B$2:$B$54</f>
+              <f>'Chart - electricity use growth'!$B$2:$B$54</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -430,7 +430,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Chart - electricity use growth '!C1</f>
+              <f>'Chart - electricity use growth'!C1</f>
             </strRef>
           </tx>
           <spPr>
@@ -451,12 +451,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - electricity use growth '!$A$2:$A$54</f>
+              <f>'Chart - electricity use growth'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - electricity use growth '!$C$2:$C$54</f>
+              <f>'Chart - electricity use growth'!$C$2:$C$54</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -466,7 +466,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Chart - electricity use growth '!D1</f>
+              <f>'Chart - electricity use growth'!D1</f>
             </strRef>
           </tx>
           <spPr>
@@ -487,12 +487,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - electricity use growth '!$A$2:$A$54</f>
+              <f>'Chart - electricity use growth'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - electricity use growth '!$D$2:$D$54</f>
+              <f>'Chart - electricity use growth'!$D$2:$D$54</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -502,7 +502,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Chart - electricity use growth '!E1</f>
+              <f>'Chart - electricity use growth'!E1</f>
             </strRef>
           </tx>
           <spPr>
@@ -523,12 +523,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - electricity use growth '!$A$2:$A$54</f>
+              <f>'Chart - electricity use growth'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - electricity use growth '!$E$2:$E$54</f>
+              <f>'Chart - electricity use growth'!$E$2:$E$54</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -538,7 +538,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Chart - electricity use growth '!F1</f>
+              <f>'Chart - electricity use growth'!F1</f>
             </strRef>
           </tx>
           <spPr>
@@ -559,12 +559,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - electricity use growth '!$A$2:$A$54</f>
+              <f>'Chart - electricity use growth'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - electricity use growth '!$F$2:$F$54</f>
+              <f>'Chart - electricity use growth'!$F$2:$F$54</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -10271,7 +10271,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>electricity use growth y/y</t>
+          <t>electricity use growth</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -10298,7 +10298,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>electricity use growth y/y</t>
+          <t>electricity use growth</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>electricity use growth y/y</t>
+          <t>electricity use growth</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>electricity use growth y/y</t>
+          <t>electricity use growth</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -10379,7 +10379,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>electricity use growth y/y</t>
+          <t>electricity use growth</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/output/Data and Chart Outputs/china_nea_consumption_monthly.xlsx
+++ b/output/Data and Chart Outputs/china_nea_consumption_monthly.xlsx
@@ -160,7 +160,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>China electricity use by sector (NEA) (to Aug/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>China electricity use by sector (NEA) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -190,12 +191,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$54</f>
+              <f>'Chart'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$54</f>
+              <f>'Chart'!$B$2:$B$55</f>
             </numRef>
           </val>
         </ser>
@@ -218,12 +219,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$54</f>
+              <f>'Chart'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$54</f>
+              <f>'Chart'!$C$2:$C$55</f>
             </numRef>
           </val>
         </ser>
@@ -246,12 +247,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$54</f>
+              <f>'Chart'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$54</f>
+              <f>'Chart'!$D$2:$D$55</f>
             </numRef>
           </val>
         </ser>
@@ -274,12 +275,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$54</f>
+              <f>'Chart'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$54</f>
+              <f>'Chart'!$E$2:$E$55</f>
             </numRef>
           </val>
         </ser>
@@ -379,7 +380,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>China electricity use growth (NEA) (to Aug/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>China electricity use growth (NEA) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -415,12 +417,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - electricity use growth'!$A$2:$A$54</f>
+              <f>'Chart - electricity use growth'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - electricity use growth'!$B$2:$B$54</f>
+              <f>'Chart - electricity use growth'!$B$2:$B$55</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -451,12 +453,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - electricity use growth'!$A$2:$A$54</f>
+              <f>'Chart - electricity use growth'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - electricity use growth'!$C$2:$C$54</f>
+              <f>'Chart - electricity use growth'!$C$2:$C$55</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -487,12 +489,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - electricity use growth'!$A$2:$A$54</f>
+              <f>'Chart - electricity use growth'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - electricity use growth'!$D$2:$D$54</f>
+              <f>'Chart - electricity use growth'!$D$2:$D$55</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -523,12 +525,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - electricity use growth'!$A$2:$A$54</f>
+              <f>'Chart - electricity use growth'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - electricity use growth'!$E$2:$E$54</f>
+              <f>'Chart - electricity use growth'!$E$2:$E$55</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -559,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - electricity use growth'!$A$2:$A$54</f>
+              <f>'Chart - electricity use growth'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - electricity use growth'!$F$2:$F$54</f>
+              <f>'Chart - electricity use growth'!$F$2:$F$55</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1062,7 +1064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1994,6 +1996,23 @@
       </c>
       <c r="E54" t="n">
         <v>188.3</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B55" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="C55" t="n">
+        <v>580</v>
+      </c>
+      <c r="D55" t="n">
+        <v>185.2</v>
+      </c>
+      <c r="E55" t="n">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -2008,7 +2027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3092,6 +3111,26 @@
       </c>
       <c r="F54" t="n">
         <v>-4</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C55" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E55" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-6</v>
       </c>
     </row>
   </sheetData>
@@ -3106,7 +3145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5546,6 +5585,51 @@
       <c r="M54" t="inlineStr">
         <is>
           <t>https://www.nea.gov.cn/20260920/bd277235282140f4b43e9e0f5f0af3d9/c.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B55" t="n">
+        <v>899.7</v>
+      </c>
+      <c r="C55" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D55" t="n">
+        <v>580</v>
+      </c>
+      <c r="E55" t="n">
+        <v>185.2</v>
+      </c>
+      <c r="F55" t="n">
+        <v>121</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H55" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J55" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>https://www.nea.gov.cn/20261021/bab7b2135e424adeaacf169cb40115ae/c.html</t>
         </is>
       </c>
     </row>
@@ -5911,7 +5995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8723,6 +8807,51 @@
       <c r="M62" t="inlineStr">
         <is>
           <t>https://www.nea.gov.cn/20260920/bd277235282140f4b43e9e0f5f0af3d9/c.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B63" t="n">
+        <v>8073.4</v>
+      </c>
+      <c r="C63" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="D63" t="n">
+        <v>5109.8</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1610.9</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1234.6</v>
+      </c>
+      <c r="G63" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H63" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I63" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J63" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K63" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>https://www.nea.gov.cn/20261021/bab7b2135e424adeaacf169cb40115ae/c.html</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10099,6 +10228,28 @@
         </is>
       </c>
       <c r="D62" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026年1-9月全社会用电量同比增长3.9%，高技术及装备制造业、充换电服务业、互联网数据服务用电量快速增长</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://www.nea.gov.cn/20261021/bab7b2135e424adeaacf169cb40115ae/c.html</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
